--- a/business-libraries/test-data/learning_problem/output_template.xlsx
+++ b/business-libraries/test-data/learning_problem/output_template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,22 +424,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>TPL-LP-RED-SUMMARY</v>
+        <v>LEARNING_PROBLEM_TPL_LP3_SUMMARY</v>
       </c>
       <c r="B2" t="str">
         <v>learning_problem</v>
       </c>
       <c r="C2" t="str">
-        <v>red</v>
+        <v>LP3</v>
       </c>
       <c r="D2" t="str">
         <v>summary</v>
       </c>
       <c r="E2" t="str">
-        <v>评估显示，您在「${维度名1}」和「${维度名2}」两个维度上的得分同时处于高危水平。注意力与策略双重薄弱，需要优先关注。</v>
+        <v>本次诊断结果为 LP3 系统干预层级，主导因素是「${主要归因}」，同时「${次要归因}」也在起作用。这个层级不适合单点施力，建议整合教师、年级和家庭支持，一次只主攻一个层面。</v>
       </c>
       <c r="F2" t="str">
-        <v>${维度名1} ${维度名2} 会被替换为实际触发红线的维度中文名</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G2" t="str">
         <v>1</v>
@@ -447,22 +447,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>TPL-LP-RED-CONCLUSION</v>
+        <v>LEARNING_PROBLEM_TPL_LP2_SUMMARY</v>
       </c>
       <c r="B3" t="str">
         <v>learning_problem</v>
       </c>
       <c r="C3" t="str">
-        <v>red</v>
+        <v>LP2</v>
       </c>
       <c r="D3" t="str">
-        <v>conclusion</v>
+        <v>summary</v>
       </c>
       <c r="E3" t="str">
-        <v>本次评估结论：${主归因}（${次归因}）。已触发安全熔断，常规建议暂停输出。</v>
+        <v>本次诊断结果为 LP2 深入诊断层级，主导因素落在「${主要归因}」。处理重点不是增加练习量，而是先结合课堂观察做交叉验证，确认卡点在哪一层。</v>
       </c>
       <c r="F3" t="str">
-        <v>${主归因} 来自归因-分级规则.主归因；${次归因} 来自归因-分级规则.次归因</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G3" t="str">
         <v>2</v>
@@ -470,99 +470,30 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>TPL-LP-RED-GOAL</v>
+        <v>LEARNING_PROBLEM_TPL_LP1_SUMMARY</v>
       </c>
       <c r="B4" t="str">
         <v>learning_problem</v>
       </c>
       <c r="C4" t="str">
-        <v>red</v>
+        <v>LP1</v>
       </c>
       <c r="D4" t="str">
-        <v>goal</v>
+        <v>summary</v>
       </c>
       <c r="E4" t="str">
-        <v>当前首要目标：1) 确保教师获得即时心理支持 2) 降低当前的急性压力水平 3) 建立至少一个可依赖的支持关系</v>
+        <v>本次诊断结果为 LP1 教师自主支持层级，主导因素是「${主要归因}」。当前可由教师通过教学策略调整自主支持，从推荐工具中选一项本周试用并记录效果。</v>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G4" t="str">
         <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>TPL-LP-ORANGE-ATTRIBUTION</v>
-      </c>
-      <c r="B5" t="str">
-        <v>learning_problem</v>
-      </c>
-      <c r="C5" t="str">
-        <v>orange</v>
-      </c>
-      <c r="D5" t="str">
-        <v>attribution</v>
-      </c>
-      <c r="E5" t="str">
-        <v>本次评估的归因分析：${主归因}。建议重点关注以下方面：${工具标签}</v>
-      </c>
-      <c r="F5" t="str">
-        <v>${主归因} ${工具标签} 从归因规则中取值</v>
-      </c>
-      <c r="G5" t="str">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>TPL-LP-ORANGE-ACTION</v>
-      </c>
-      <c r="B6" t="str">
-        <v>learning_problem</v>
-      </c>
-      <c r="C6" t="str">
-        <v>orange</v>
-      </c>
-      <c r="D6" t="str">
-        <v>action</v>
-      </c>
-      <c r="E6" t="str">
-        <v>根据评估结果，建议采取以下行动：${输出动作摘要}。推荐工具：${输出工具摘要}。</v>
-      </c>
-      <c r="F6" t="str">
-        <v>${输出动作摘要} ${输出工具摘要} 从归因规则中取值</v>
-      </c>
-      <c r="G6" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>TPL-LP-GREEN-SUMMARY</v>
-      </c>
-      <c r="B7" t="str">
-        <v>learning_problem</v>
-      </c>
-      <c r="C7" t="str">
-        <v>green</v>
-      </c>
-      <c r="D7" t="str">
-        <v>summary</v>
-      </c>
-      <c r="E7" t="str">
-        <v>本次评估结果整体良好，各项指标均在正常范围内。继续保持现有节奏。</v>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/learning_problem/output_template.xlsx
+++ b/business-libraries/test-data/learning_problem/output_template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,22 +424,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>LEARNING_PROBLEM_TPL_LP3_SUMMARY</v>
+        <v>TPL_LP_RED_1</v>
       </c>
       <c r="B2" t="str">
         <v>learning_problem</v>
       </c>
       <c r="C2" t="str">
-        <v>LP3</v>
+        <v>red</v>
       </c>
       <c r="D2" t="str">
         <v>summary</v>
       </c>
       <c r="E2" t="str">
-        <v>本次诊断结果为 LP3 系统干预层级，主导因素是「${主要归因}」，同时「${次要归因}」也在起作用。这个层级不适合单点施力，建议整合教师、年级和家庭支持，一次只主攻一个层面。</v>
+        <v>评估显示该生的学习问题已达到需要专业介入的程度，常规教学支持已不足够。请转介心理专员或学习支持中心，并与家长同步情况。</v>
       </c>
       <c r="F2" t="str">
-        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
+        <v>可用占位符见 ⑩ 说明</v>
       </c>
       <c r="G2" t="str">
         <v>1</v>
@@ -447,22 +447,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>LEARNING_PROBLEM_TPL_LP2_SUMMARY</v>
+        <v>TPL_LP_ORANGE_2</v>
       </c>
       <c r="B3" t="str">
         <v>learning_problem</v>
       </c>
       <c r="C3" t="str">
-        <v>LP2</v>
+        <v>orange</v>
       </c>
       <c r="D3" t="str">
         <v>summary</v>
       </c>
       <c r="E3" t="str">
-        <v>本次诊断结果为 LP2 深入诊断层级，主导因素落在「${主要归因}」。处理重点不是增加练习量，而是先结合课堂观察做交叉验证，确认卡点在哪一层。</v>
+        <v>本次诊断结果为 LP3 系统干预层级，主导因素是「${主要归因}」，同时「${次要归因}」也在起作用。这个层级不适合单点施力，建议整合教师、年级和家庭支持，一次只主攻一个层面。</v>
       </c>
       <c r="F3" t="str">
-        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
+        <v>可用占位符见 ⑩ 说明</v>
       </c>
       <c r="G3" t="str">
         <v>2</v>
@@ -470,30 +470,53 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>LEARNING_PROBLEM_TPL_LP1_SUMMARY</v>
+        <v>TPL_LP_YELLOW_3</v>
       </c>
       <c r="B4" t="str">
         <v>learning_problem</v>
       </c>
       <c r="C4" t="str">
-        <v>LP1</v>
+        <v>yellow</v>
       </c>
       <c r="D4" t="str">
         <v>summary</v>
       </c>
       <c r="E4" t="str">
-        <v>本次诊断结果为 LP1 教师自主支持层级，主导因素是「${主要归因}」。当前可由教师通过教学策略调整自主支持，从推荐工具中选一项本周试用并记录效果。</v>
+        <v>本次诊断结果为 LP2 深入诊断层级，主导因素落在「${主要归因}」。处理重点不是增加练习量，而是先结合课堂观察做交叉验证，确认卡点在哪一层。</v>
       </c>
       <c r="F4" t="str">
-        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
+        <v>可用占位符见 ⑩ 说明</v>
       </c>
       <c r="G4" t="str">
         <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>TPL_LP_DEFAULT</v>
+      </c>
+      <c r="B5" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="C5" t="str">
+        <v>green</v>
+      </c>
+      <c r="D5" t="str">
+        <v>summary</v>
+      </c>
+      <c r="E5" t="str">
+        <v>本次诊断结果为 LP1 教师自主支持层级，主导因素是「${主要归因}」。当前可由教师通过教学策略调整自主支持，从推荐工具中选一项本周试用并记录效果。</v>
+      </c>
+      <c r="F5" t="str">
+        <v>兜底模板：命中未覆盖等级时使用</v>
+      </c>
+      <c r="G5" t="str">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/learning_problem/output_template.xlsx
+++ b/business-libraries/test-data/learning_problem/output_template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,22 +424,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>TPL_LP_RED_1</v>
+        <v>LEARNING_PROBLEM_TPL_LP3_SUMMARY</v>
       </c>
       <c r="B2" t="str">
         <v>learning_problem</v>
       </c>
       <c r="C2" t="str">
-        <v>red</v>
+        <v>LP3</v>
       </c>
       <c r="D2" t="str">
         <v>summary</v>
       </c>
       <c r="E2" t="str">
-        <v>评估显示该生的学习问题已达到需要专业介入的程度，常规教学支持已不足够。请转介心理专员或学习支持中心，并与家长同步情况。</v>
+        <v>本次诊断结果为 LP3 系统干预层级，主导因素是「${主要归因}」，同时「${次要归因}」也在起作用。这个层级不适合单点施力，建议整合教师、年级和家庭支持，一次只主攻一个层面。</v>
       </c>
       <c r="F2" t="str">
-        <v>可用占位符见 ⑩ 说明</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G2" t="str">
         <v>1</v>
@@ -447,22 +447,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>TPL_LP_ORANGE_2</v>
+        <v>LEARNING_PROBLEM_TPL_LP2_SUMMARY</v>
       </c>
       <c r="B3" t="str">
         <v>learning_problem</v>
       </c>
       <c r="C3" t="str">
-        <v>orange</v>
+        <v>LP2</v>
       </c>
       <c r="D3" t="str">
         <v>summary</v>
       </c>
       <c r="E3" t="str">
-        <v>本次诊断结果为 LP3 系统干预层级，主导因素是「${主要归因}」，同时「${次要归因}」也在起作用。这个层级不适合单点施力，建议整合教师、年级和家庭支持，一次只主攻一个层面。</v>
+        <v>本次诊断结果为 LP2 深入诊断层级，主导因素落在「${主要归因}」。处理重点不是增加练习量，而是先结合课堂观察做交叉验证，确认卡点在哪一层。</v>
       </c>
       <c r="F3" t="str">
-        <v>可用占位符见 ⑩ 说明</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G3" t="str">
         <v>2</v>
@@ -470,53 +470,30 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>TPL_LP_YELLOW_3</v>
+        <v>LEARNING_PROBLEM_TPL_LP1_SUMMARY</v>
       </c>
       <c r="B4" t="str">
         <v>learning_problem</v>
       </c>
       <c r="C4" t="str">
-        <v>yellow</v>
+        <v>LP1</v>
       </c>
       <c r="D4" t="str">
         <v>summary</v>
       </c>
       <c r="E4" t="str">
-        <v>本次诊断结果为 LP2 深入诊断层级，主导因素落在「${主要归因}」。处理重点不是增加练习量，而是先结合课堂观察做交叉验证，确认卡点在哪一层。</v>
+        <v>本次诊断结果为 LP1 教师自主支持层级，主导因素是「${主要归因}」。当前可由教师通过教学策略调整自主支持，从推荐工具中选一项本周试用并记录效果。</v>
       </c>
       <c r="F4" t="str">
-        <v>可用占位符见 ⑩ 说明</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G4" t="str">
         <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>TPL_LP_DEFAULT</v>
-      </c>
-      <c r="B5" t="str">
-        <v>learning_problem</v>
-      </c>
-      <c r="C5" t="str">
-        <v>green</v>
-      </c>
-      <c r="D5" t="str">
-        <v>summary</v>
-      </c>
-      <c r="E5" t="str">
-        <v>本次诊断结果为 LP1 教师自主支持层级，主导因素是「${主要归因}」。当前可由教师通过教学策略调整自主支持，从推荐工具中选一项本周试用并记录效果。</v>
-      </c>
-      <c r="F5" t="str">
-        <v>兜底模板：命中未覆盖等级时使用</v>
-      </c>
-      <c r="G5" t="str">
-        <v>99</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/learning_problem/output_template.xlsx
+++ b/business-libraries/test-data/learning_problem/output_template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,7 +436,7 @@
         <v>summary</v>
       </c>
       <c r="E2" t="str">
-        <v>评估显示该生的学习问题已达到需要专业介入的程度，常规教学支持已不足够。请转介心理专员或学习支持中心，并与家长同步情况。</v>
+        <v>SNAP-IV 筛查提示该生可能存在注意缺陷或多动-冲动样表现（任一组≥6项≥2分）。本量表仅作筛查预警，不作临床诊断：请先结合课堂观察交叉核实，并与家长沟通后转介心理教师或专业机构进一步评估，同步开展认知剖面分析。</v>
       </c>
       <c r="F2" t="str">
         <v>可用占位符见 ⑩ 说明</v>
@@ -459,7 +459,7 @@
         <v>summary</v>
       </c>
       <c r="E3" t="str">
-        <v>本次诊断结果为 LP3 系统干预层级，主导因素是「${主要归因}」，同时「${次要归因}」也在起作用。这个层级不适合单点施力，建议整合教师、年级和家庭支持，一次只主攻一个层面。</v>
+        <v>学业情绪评估显示消极情绪偏多（焦虑/无聊/羞耻）或积极情绪明显不足，可能存在情绪性学习困难。请优先疏导情绪（团体辅导、家长指导），再谈学习策略与方法，避免把情绪问题当成态度问题处理。</v>
       </c>
       <c r="F3" t="str">
         <v>可用占位符见 ⑩ 说明</v>
@@ -482,7 +482,7 @@
         <v>summary</v>
       </c>
       <c r="E4" t="str">
-        <v>本次诊断结果为 LP2 深入诊断层级，主导因素落在「${主要归因}」。处理重点不是增加练习量，而是先结合课堂观察做交叉验证，确认卡点在哪一层。</v>
+        <v>学习策略评估显示策略使用薄弱（总均分≤2.5）。建议从计划、监控等元认知策略入手，配合学科辅导策略开展专项支持，避免只加练习量。</v>
       </c>
       <c r="F4" t="str">
         <v>可用占位符见 ⑩ 说明</v>
@@ -493,30 +493,53 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>TPL_LP_DEFAULT</v>
+        <v>TPL_LP_BLUE_4</v>
       </c>
       <c r="B5" t="str">
         <v>learning_problem</v>
       </c>
       <c r="C5" t="str">
-        <v>green</v>
+        <v>blue</v>
       </c>
       <c r="D5" t="str">
         <v>summary</v>
       </c>
       <c r="E5" t="str">
-        <v>本次诊断结果为 LP1 教师自主支持层级，主导因素是「${主要归因}」。当前可由教师通过教学策略调整自主支持，从推荐工具中选一项本周试用并记录效果。</v>
+        <v>成绩趋势显示存在薄弱或下滑信号（低于班级均值或连续下滑）。请结合归因进一步定位是知识断层、策略缺失还是其他因素；多科同时下滑时优先排查家庭与情绪因素。</v>
       </c>
       <c r="F5" t="str">
+        <v>可用占位符见 ⑩ 说明</v>
+      </c>
+      <c r="G5" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>TPL_LP_DEFAULT</v>
+      </c>
+      <c r="B6" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="C6" t="str">
+        <v>green</v>
+      </c>
+      <c r="D6" t="str">
+        <v>summary</v>
+      </c>
+      <c r="E6" t="str">
+        <v>本次评估暂未发现需要重点干预的学习问题信号，当前状态相对平稳，建议保持现有节奏，持续观察课堂表现与成绩趋势。</v>
+      </c>
+      <c r="F6" t="str">
         <v>兜底模板：命中未覆盖等级时使用</v>
       </c>
-      <c r="G5" t="str">
+      <c r="G6" t="str">
         <v>99</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
   </ignoredErrors>
 </worksheet>
 </file>